--- a/excel/calculadora_IT_OT.xlsx
+++ b/excel/calculadora_IT_OT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupstucom-my.sharepoint.com/personal/llorenc_huguet_365_stucom_com/Documents/Documentos/GitHub/Digitalizacion/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="480" documentId="8_{664E4ED6-0F2D-414E-8487-EF42C32A33C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{854365C9-9EB5-4963-A897-B20B3B73C186}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{8D7EFD2A-C651-438E-BF61-642E294B9AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{338388CC-15DA-4B4C-8723-3A6989797905}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-8865" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supuestos" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,10 @@
     <sheet name="ORG-DIG-07" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ORG-DIG-02'!$F$1:$F$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ORG-DIG-07'!$F$1:$F$23</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="2">'ORG-DIG-02'!$B$12</definedName>
-    <definedName name="_xlnm.Extract" localSheetId="3">'ORG-DIG-07'!$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ORG-DIG-02'!$F$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ORG-DIG-07'!$F$1:$F$24</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="2">'ORG-DIG-02'!$B$13</definedName>
+    <definedName name="_xlnm.Extract" localSheetId="3">'ORG-DIG-07'!$B$13</definedName>
     <definedName name="MaxCol">Supuestos!$C$4:$C$6</definedName>
     <definedName name="MedCol">Supuestos!$D$4:$D$6</definedName>
     <definedName name="MinCol">Supuestos!$B$4:$B$6</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="159">
   <si>
     <t>Rangos de tarifa por tipo de consultor (España, IT/OT)</t>
   </si>
@@ -520,13 +520,17 @@
   </si>
   <si>
     <t>Selecciona tecnología principal</t>
+  </si>
+  <si>
+    <t>Calculo de costos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -731,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -759,6 +763,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -813,10 +819,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,12 +1205,12 @@
         <f>AVERAGE(B5:C5)</f>
         <v>67.5</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -1224,28 +1226,28 @@
         <f>AVERAGE(B6:C6)</f>
         <v>107.5</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="18"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
@@ -1645,7 +1647,7 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>21</v>
@@ -1659,7 +1661,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -1710,7 +1712,7 @@
       </c>
       <c r="B9" s="4">
         <f>IF(B6="Personalizada", B7, IF(B6="Mín", INDEX(MinCol, MATCH(B4, Tipos, 0)), IF(B6="Máx", INDEX(MaxCol, MATCH(B4, Tipos, 0)), INDEX(MedCol, MATCH(B4, Tipos, 0)))))</f>
-        <v>95</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1719,7 +1721,7 @@
       </c>
       <c r="B10" s="4">
         <f>B5*B9</f>
-        <v>95</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1745,15 +1747,15 @@
       </c>
       <c r="B14" s="4">
         <f>INDEX(MinCol, MATCH(B4, Tipos, 0))</f>
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C14" s="4">
         <f>INDEX(MedCol, MATCH(B4, Tipos, 0))</f>
-        <v>107.5</v>
+        <v>42.5</v>
       </c>
       <c r="D14" s="4">
         <f>INDEX(MaxCol, MATCH(B4, Tipos, 0))</f>
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1762,15 +1764,15 @@
       </c>
       <c r="B15" s="4">
         <f>B5*B14</f>
-        <v>95</v>
+        <v>420</v>
       </c>
       <c r="C15" s="4">
         <f>B5*C14</f>
-        <v>107.5</v>
+        <v>510</v>
       </c>
       <c r="D15" s="4">
         <f>B5*D14</f>
-        <v>120</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
@@ -1805,7 +1807,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A7E1EF-D4A3-433E-AB47-0E3539979D43}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.77734375" customWidth="1"/>
@@ -1861,13 +1863,13 @@
         <v>144</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="F4" s="15"/>
       <c r="H4" s="11" t="s">
@@ -1895,13 +1897,13 @@
         <v>125</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="E7" s="11"/>
       <c r="H7" s="12" t="s">
@@ -1910,17 +1912,17 @@
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="18" t="s">
         <v>126</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="F8" s="15"/>
       <c r="H8" s="11" t="s">
@@ -1929,297 +1931,308 @@
       <c r="J8"/>
     </row>
     <row r="9" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2190</v>
+      </c>
       <c r="F9" s="15"/>
       <c r="H9" s="11" t="s">
         <v>119</v>
       </c>
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="17"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="11"/>
-      <c r="H10" s="11" t="s">
+      <c r="B11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="H11" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="F11" s="15"/>
-      <c r="H11" t="s">
+    <row r="12" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="F12" s="15"/>
+      <c r="H12" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="11"/>
-      <c r="H12" s="11" t="s">
+      <c r="B13" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="H13" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="F13" s="15"/>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+    <row r="14" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="F14" s="15"/>
+      <c r="H14"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>136</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>137</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>138</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="H14" s="12" t="s">
+      <c r="E15" s="11"/>
+      <c r="H15" s="12" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="H15" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
-      <c r="B16" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" t="s">
-        <v>141</v>
+      <c r="B16" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="F16" s="15"/>
       <c r="H16" s="11" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
-      <c r="B17" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>129</v>
+      <c r="B17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" t="s">
+        <v>141</v>
       </c>
       <c r="F17" s="15"/>
       <c r="H17" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
+      <c r="B18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>102</v>
+      </c>
       <c r="F18" s="15"/>
       <c r="H18" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="F19" s="15"/>
+      <c r="H19" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="16"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="16"/>
-      <c r="F20" s="15"/>
-      <c r="H20" s="12" t="s">
-        <v>156</v>
-      </c>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="16"/>
       <c r="F21" s="15"/>
-      <c r="H21" s="11" t="s">
-        <v>129</v>
+      <c r="H21" s="12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
       <c r="H22" s="11" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="16"/>
       <c r="F23" s="15"/>
       <c r="H23" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="15"/>
+      <c r="H24" s="11" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="16"/>
-      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
       <c r="E25" s="16"/>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="16"/>
+      <c r="H26" s="12" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="16"/>
-      <c r="H26" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
+      <c r="A27" s="13"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="16"/>
       <c r="H27" s="11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>134</v>
-      </c>
+      <c r="A28" s="11"/>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="H28" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="H29" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C30" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H30" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="14"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="14"/>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="14"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B19:D26"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B20:D27"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:D13" xr:uid="{BC2E7F79-7354-42B6-B8D9-768A0B5A0E48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:D14" xr:uid="{BC2E7F79-7354-42B6-B8D9-768A0B5A0E48}">
       <formula1>$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:D7" xr:uid="{E8B01BEA-0B81-46AF-B906-74201A40FEAD}">
-      <formula1>$H$15:$H$18</formula1>
+      <formula1>$H$16:$H$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12:D12" xr:uid="{AC1FD742-9F25-4281-9812-BFB96C597D39}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:D13" xr:uid="{AC1FD742-9F25-4281-9812-BFB96C597D39}">
       <formula1>$H$2:$H$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:D4 B8:D8 B15:D15 B17:D17" xr:uid="{4C2CD737-4FAA-4A89-BE74-865DEBFE4AED}">
-      <formula1>$H$21:$H$23</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:D4 B18:D18 B16:D16 B8:D8" xr:uid="{4C2CD737-4FAA-4A89-BE74-865DEBFE4AED}">
+      <formula1>$H$22:$H$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:D11" xr:uid="{26E71B58-CF50-4D67-A67B-1F3D006BAB8D}">
-      <formula1>$H$26:$H$29</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:D12" xr:uid="{26E71B58-CF50-4D67-A67B-1F3D006BAB8D}">
+      <formula1>$H$27:$H$30</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2228,8 +2241,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B2826F6-22F6-4B80-AACB-771619D05E13}">
-  <dimension ref="A1:J32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.6640625" style="11" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="11" customWidth="1"/>
@@ -2338,273 +2351,279 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0</v>
+      </c>
       <c r="H9" s="11" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="11" t="s">
+      <c r="B11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="H11" s="11" t="s">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="H12" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="11" t="s">
+      <c r="B13" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-    </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="12"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B15" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C15" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H15" s="12" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
       <c r="B16" s="11" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="11" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12"/>
+      <c r="B18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>129</v>
+      </c>
       <c r="H18" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="H19" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="16"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="24"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
       <c r="E20" s="16"/>
-      <c r="H20" s="12" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="16"/>
-      <c r="H21" s="11" t="s">
-        <v>129</v>
+      <c r="H21" s="12" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
       <c r="E22" s="16"/>
       <c r="H22" s="11" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="24"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="16"/>
       <c r="H23" s="11" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="24"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="26"/>
       <c r="E24" s="16"/>
+      <c r="H24" s="11" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
       <c r="E25" s="16"/>
-      <c r="H25" s="12" t="s">
-        <v>109</v>
-      </c>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="27"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="26"/>
       <c r="E26" s="16"/>
-      <c r="H26" s="11" t="s">
-        <v>129</v>
+      <c r="H26" s="12" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="16"/>
       <c r="H27" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H28" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H29" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C30" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H30" s="11" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="14"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="14"/>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="14"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B19:D26"/>
-    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="B20:D27"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12:D12" xr:uid="{35B7167B-493D-467B-9CE3-11F2BCF619C9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:D13" xr:uid="{35B7167B-493D-467B-9CE3-11F2BCF619C9}">
       <formula1>$H$2:$H$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B7:D7" xr:uid="{91967A11-D29D-4841-8044-6AD44DA8A6AC}">
-      <formula1>$H$15:$H$18</formula1>
+      <formula1>$H$16:$H$19</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:D13" xr:uid="{E8E3BD6B-9E1C-485E-9B49-99A767ACD6FE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:D14" xr:uid="{E8E3BD6B-9E1C-485E-9B49-99A767ACD6FE}">
       <formula1>$H$2:$H$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10:D11" xr:uid="{8699104E-A017-4A85-B308-2E1BFC352EF4}">
-      <formula1>$H$26:$H$29</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:D12" xr:uid="{8699104E-A017-4A85-B308-2E1BFC352EF4}">
+      <formula1>$H$27:$H$30</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:D4 B17:D17 B15:D15" xr:uid="{E3B60488-97C3-4CBB-924D-CB300356DAF9}">
-      <formula1>$H$21:$H$23</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:D4 B16:D16 B18:D18" xr:uid="{E3B60488-97C3-4CBB-924D-CB300356DAF9}">
+      <formula1>$H$22:$H$24</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8:D8" xr:uid="{09B8C2F6-84D7-448D-A03D-D950622DA122}">
-      <formula1>$H$8:$H$13</formula1>
+      <formula1>$H$8:$H$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
